--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="10080" windowHeight="5145"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>编号</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>登录成功</t>
+  </si>
+  <si>
+    <t>select mg_name from sp_manager where mg_name="admin"</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
   <si>
     <t>用户管理</t>
@@ -1156,7 +1162,8 @@
     <col min="4" max="4" width="29.625" customWidth="1"/>
     <col min="8" max="8" width="28.25" customWidth="1"/>
     <col min="9" max="9" width="44.875" customWidth="1"/>
-    <col min="14" max="15" width="15" customWidth="1"/>
+    <col min="14" max="14" width="58.25" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="11.5" customWidth="1"/>
     <col min="17" max="17" width="10.375" customWidth="1"/>
   </cols>
@@ -1301,6 +1308,12 @@
       <c r="M3" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="N3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="R3" s="2" t="b">
         <v>1</v>
       </c>
@@ -1310,28 +1323,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>1</v>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10080" windowHeight="5145"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>编号</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>admin</t>
+  </si>
+  <si>
+    <t>{"TOKEN":"$..token"}</t>
   </si>
   <si>
     <t>用户管理</t>
@@ -1164,7 +1167,7 @@
     <col min="9" max="9" width="44.875" customWidth="1"/>
     <col min="14" max="14" width="58.25" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="16" max="16" width="22.625" customWidth="1"/>
     <col min="17" max="17" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1314,6 +1317,9 @@
       <c r="O3" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="P3" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="R3" s="2" t="b">
         <v>1</v>
       </c>
@@ -1323,28 +1329,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>1</v>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="17580" windowHeight="5730"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>编号</t>
   </si>
@@ -177,6 +177,9 @@
     <t>{"TOKEN":"$..token"}</t>
   </si>
   <si>
+    <t>{"ADMIN_NAME":"select mg_name from sp_manager where mg_name='admin'"}</t>
+  </si>
+  <si>
     <t>用户管理</t>
   </si>
   <si>
@@ -196,6 +199,9 @@
   </si>
   <si>
     <t>无效token</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1158,8 +1164,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="29.625" customWidth="1"/>
@@ -1168,7 +1174,7 @@
     <col min="14" max="14" width="58.25" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="22.625" customWidth="1"/>
-    <col min="17" max="17" width="10.375" customWidth="1"/>
+    <col min="17" max="17" width="77.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:18">
@@ -1320,6 +1326,9 @@
       <c r="P3" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="Q3" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="R3" s="2" t="b">
         <v>1</v>
       </c>
@@ -1329,31 +1338,36 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="P6" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>编号</t>
   </si>
@@ -199,6 +199,21 @@
   </si>
   <si>
     <t>无效token</t>
+  </si>
+  <si>
+    <t>查询成功</t>
+  </si>
+  <si>
+    <t>查询用户数据列表成功</t>
+  </si>
+  <si>
+    <t>{"Authorization":"{{TOKEN}}"}</t>
+  </si>
+  <si>
+    <t>{"pagenum":1,"pagesize":2}</t>
+  </si>
+  <si>
+    <t>获取管理员列表成功</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -1169,8 +1184,11 @@
   <cols>
     <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="29.625" customWidth="1"/>
+    <col min="7" max="7" width="32.625" customWidth="1"/>
     <col min="8" max="8" width="28.25" customWidth="1"/>
     <col min="9" max="9" width="44.875" customWidth="1"/>
+    <col min="12" max="12" width="9.375" customWidth="1"/>
+    <col min="13" max="13" width="19.125" customWidth="1"/>
     <col min="14" max="14" width="58.25" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="22.625" customWidth="1"/>
@@ -1365,9 +1383,44 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" s="2" customFormat="1" spans="1:18">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="6" spans="1:18">
       <c r="P6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17580" windowHeight="5730"/>
+    <workbookView windowWidth="9840" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t>编号</t>
   </si>
@@ -210,13 +210,52 @@
     <t>{"Authorization":"{{TOKEN}}"}</t>
   </si>
   <si>
-    <t>{"pagenum":1,"pagesize":2}</t>
-  </si>
-  <si>
     <t>获取管理员列表成功</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>新增成功</t>
+  </si>
+  <si>
+    <t>添加一个用户，添加成功</t>
+  </si>
+  <si>
+    <t>{"username":"meiqi","password":"123456"}</t>
+  </si>
+  <si>
+    <t>创建成功</t>
+  </si>
+  <si>
+    <t>{"MEIQI_ID":"$..id"}</t>
+  </si>
+  <si>
+    <t>修改成功</t>
+  </si>
+  <si>
+    <t>修改用户状态，修改成功</t>
+  </si>
+  <si>
+    <t>put</t>
+  </si>
+  <si>
+    <t>/users/{{MEIQI_ID}}/state/true</t>
+  </si>
+  <si>
+    <t>设置状态成功</t>
+  </si>
+  <si>
+    <t>图片上传</t>
+  </si>
+  <si>
+    <t>上传成功</t>
+  </si>
+  <si>
+    <t>图片上传成功</t>
+  </si>
+  <si>
+    <t>/upload</t>
+  </si>
+  <si>
+    <t>{"file":("1.jpg",open("./file/1.jpg","rb"),"jpg")}</t>
   </si>
 </sst>
 </file>
@@ -1179,14 +1218,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="29.625" customWidth="1"/>
+    <col min="6" max="6" width="33.75" customWidth="1"/>
     <col min="7" max="7" width="32.625" customWidth="1"/>
     <col min="8" max="8" width="28.25" customWidth="1"/>
     <col min="9" max="9" width="44.875" customWidth="1"/>
+    <col min="11" max="11" width="53.75" customWidth="1"/>
     <col min="12" max="12" width="9.375" customWidth="1"/>
     <col min="13" max="13" width="19.125" customWidth="1"/>
     <col min="14" max="14" width="58.25" customWidth="1"/>
@@ -1373,9 +1414,6 @@
       <c r="H4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M4" s="2" t="s">
         <v>54</v>
       </c>
@@ -1406,21 +1444,117 @@
         <v>57</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="P6" t="s">
+    <row r="6" s="2" customFormat="1" spans="1:18">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:18">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:18">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
